--- a/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,39 +634,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 14,19</t>
+          <t>-24,41; 16,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 0,91</t>
+          <t>-40,68; 0,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 38,68</t>
+          <t>-6,33; 37,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 40,62</t>
+          <t>-44,11; 46,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,04; 4,46</t>
+          <t>-58,9; 1,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 301,01</t>
+          <t>-27,97; 281,13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,39 +714,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 3,66</t>
+          <t>-21,94; 3,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 1,64</t>
+          <t>-25,21; 1,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,49; 7,51</t>
+          <t>-47,33; 7,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 8,12</t>
+          <t>-39,46; 8,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,59; 4,0</t>
+          <t>-42,11; 3,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,31; 22,43</t>
+          <t>-86,86; 27,06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 18,81</t>
+          <t>-16,34; 18,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 10,68</t>
+          <t>-19,26; 9,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-48,73; -5,07</t>
+          <t>-47,83; -3,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,59; 42,75</t>
+          <t>-24,6; 43,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 35,46</t>
+          <t>-43,57; 35,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,17; -10,53</t>
+          <t>-78,17; -8,97</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,56; -0,56</t>
+          <t>-31,71; -0,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 7,27</t>
+          <t>-28,67; 8,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,25; 1,57</t>
+          <t>-68,11; -0,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,39; -0,93</t>
+          <t>-52,15; -1,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,6; 18,66</t>
+          <t>-52,64; 22,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,84; 8,97</t>
+          <t>-88,12; 2,28</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 17,55</t>
+          <t>-29,38; 13,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 11,01</t>
+          <t>-27,04; 10,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 16,87</t>
+          <t>-26,67; 15,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 39,37</t>
+          <t>-47,42; 32,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 44,52</t>
+          <t>-59,79; 40,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 44,9</t>
+          <t>-45,15; 43,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1034,39 +1034,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 23,09</t>
+          <t>-12,84; 21,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -0,38</t>
+          <t>-34,93; -1,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 4,07</t>
+          <t>-37,09; 5,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 80,09</t>
+          <t>-26,87; 72,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,52; -0,13</t>
+          <t>-61,86; -2,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,69; 26,2</t>
+          <t>-86,9; 36,21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,42; -6,41</t>
+          <t>-29,74; -6,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 0,53</t>
+          <t>-20,35; 1,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 7,75</t>
+          <t>-26,59; 7,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-46,51; -12,48</t>
+          <t>-46,45; -12,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 1,92</t>
+          <t>-50,07; 4,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 20,21</t>
+          <t>-49,59; 19,2</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 5,32</t>
+          <t>-18,12; 3,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 1,27</t>
+          <t>-18,33; 1,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,2; -3,38</t>
+          <t>-32,28; -2,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 9,83</t>
+          <t>-27,67; 6,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 2,86</t>
+          <t>-33,98; 3,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,94; -5,5</t>
+          <t>-70,26; -8,33</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -4,07</t>
+          <t>-13,83; -3,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -5,62</t>
+          <t>-15,46; -5,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -4,79</t>
+          <t>-22,81; -4,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -7,88</t>
+          <t>-24,72; -6,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-32,25; -13,07</t>
+          <t>-32,46; -13,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-56,09; -13,85</t>
+          <t>-54,39; -13,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 16,3</t>
+          <t>-25,55; 15,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 0,2</t>
+          <t>-43,52; -0,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 37,04</t>
+          <t>-6,91; 38,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 46,76</t>
+          <t>-45,08; 43,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,9; 1,82</t>
+          <t>-62,13; -1,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 281,13</t>
+          <t>-26,65; 329,79</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 3,99</t>
+          <t>-23,07; 2,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 1,73</t>
+          <t>-25,07; 0,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 7,7</t>
+          <t>-43,87; 8,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 8,31</t>
+          <t>-41,28; 7,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 3,56</t>
+          <t>-41,98; 1,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,86; 27,06</t>
+          <t>-85,03; 27,48</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 18,6</t>
+          <t>-13,0; 19,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 9,58</t>
+          <t>-21,3; 9,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,83; -3,84</t>
+          <t>-47,48; -5,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 43,53</t>
+          <t>-22,16; 43,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 35,12</t>
+          <t>-48,04; 32,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,17; -8,97</t>
+          <t>-77,94; -12,0</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,71; -0,79</t>
+          <t>-31,74; 0,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 8,83</t>
+          <t>-27,96; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,11; -0,1</t>
+          <t>-66,27; 2,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,15; -1,44</t>
+          <t>-50,91; 0,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 22,3</t>
+          <t>-51,06; 20,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,12; 2,28</t>
+          <t>-87,29; 14,32</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 13,89</t>
+          <t>-30,15; 15,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 10,23</t>
+          <t>-26,97; 9,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 15,53</t>
+          <t>-31,01; 13,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 32,25</t>
+          <t>-46,62; 32,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,79; 40,74</t>
+          <t>-60,75; 38,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 43,86</t>
+          <t>-48,96; 36,13</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 21,39</t>
+          <t>-13,65; 21,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,93; -1,2</t>
+          <t>-35,52; -2,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 5,41</t>
+          <t>-40,43; 3,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 72,78</t>
+          <t>-29,3; 69,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,86; -2,81</t>
+          <t>-63,12; -3,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,9; 36,21</t>
+          <t>-87,7; 25,31</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,74; -6,81</t>
+          <t>-30,55; -7,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 1,21</t>
+          <t>-19,76; 0,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 7,41</t>
+          <t>-25,9; 8,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-46,45; -12,69</t>
+          <t>-47,15; -12,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 4,69</t>
+          <t>-48,0; 3,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 19,2</t>
+          <t>-50,15; 25,28</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 3,31</t>
+          <t>-17,33; 3,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 1,61</t>
+          <t>-19,02; 1,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,28; -2,38</t>
+          <t>-30,87; -2,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 6,5</t>
+          <t>-27,6; 7,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 3,14</t>
+          <t>-34,91; 3,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,26; -8,33</t>
+          <t>-67,36; -8,29</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -3,64</t>
+          <t>-13,42; -3,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,62</t>
+          <t>-15,46; -5,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,81; -4,82</t>
+          <t>-22,53; -4,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,72; -6,86</t>
+          <t>-23,66; -7,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -13,35</t>
+          <t>-32,44; -12,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-54,39; -13,64</t>
+          <t>-51,72; -12,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,72</t>
+          <t>9,31</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 15,44</t>
+          <t>-25,47; 14,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-43,52; -0,88</t>
+          <t>-39,44; 0,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 38,33</t>
+          <t>-10,06; 30,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 43,98</t>
+          <t>-46,51; 40,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,13; -1,47</t>
+          <t>-57,04; 4,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 329,79</t>
+          <t>-35,79; 234,48</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-16,75</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-42,5%</t>
+          <t>-19,12%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 2,89</t>
+          <t>-21,83; 3,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 0,59</t>
+          <t>-25,6; 1,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,87; 8,61</t>
+          <t>-30,33; 12,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 7,2</t>
+          <t>-38,36; 8,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 1,49</t>
+          <t>-42,59; 4,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,03; 27,48</t>
+          <t>-58,16; 48,81</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-27,49</t>
+          <t>-27,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-52,84%</t>
+          <t>-51,88%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 19,38</t>
+          <t>-14,31; 18,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 9,63</t>
+          <t>-20,35; 10,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -5,06</t>
+          <t>-48,05; -3,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 43,92</t>
+          <t>-23,59; 42,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 32,39</t>
+          <t>-45,79; 35,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,94; -12,0</t>
+          <t>-77,38; -8,36</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-36,98</t>
+          <t>-35,63</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-61,33%</t>
+          <t>-60,11%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 0,08</t>
+          <t>-31,56; -0,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 7,76</t>
+          <t>-28,53; 7,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,27; 2,04</t>
+          <t>-67,58; 3,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 0,23</t>
+          <t>-51,39; -0,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 20,32</t>
+          <t>-51,6; 18,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,29; 14,32</t>
+          <t>-90,03; 21,03</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,44</t>
+          <t>-7,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,96%</t>
+          <t>-14,31%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 15,35</t>
+          <t>-28,62; 17,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 9,48</t>
+          <t>-25,9; 11,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 13,48</t>
+          <t>-27,62; 16,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 32,39</t>
+          <t>-45,14; 39,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,75; 38,24</t>
+          <t>-58,54; 44,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 36,13</t>
+          <t>-48,25; 44,35</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-18,49</t>
+          <t>-17,41</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-53,65%</t>
+          <t>-52,41%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 21,54</t>
+          <t>-11,97; 23,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,52; -2,09</t>
+          <t>-35,28; -0,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 3,99</t>
+          <t>-36,71; 4,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 69,21</t>
+          <t>-24,43; 80,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,12; -3,69</t>
+          <t>-62,52; -0,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,7; 25,31</t>
+          <t>-88,67; 29,74</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,49</t>
+          <t>-12,88</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-20,74%</t>
+          <t>-28,45%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,55; -7,03</t>
+          <t>-29,42; -6,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 0,6</t>
+          <t>-19,32; 0,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 8,81</t>
+          <t>-29,66; 3,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -12,4</t>
+          <t>-46,51; -12,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 3,11</t>
+          <t>-49,36; 1,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 25,28</t>
+          <t>-56,61; 10,49</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-18,08</t>
+          <t>-18,86</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,88%</t>
+          <t>-48,41%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 3,91</t>
+          <t>-16,26; 5,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 1,19</t>
+          <t>-18,5; 1,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -2,81</t>
+          <t>-33,0; -4,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 7,29</t>
+          <t>-26,24; 9,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 3,14</t>
+          <t>-33,98; 2,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,36; -8,29</t>
+          <t>-71,31; -7,45</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-13,31</t>
+          <t>-13,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-32,43%</t>
+          <t>-31,92%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,42; -3,61</t>
+          <t>-14,05; -4,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,53</t>
+          <t>-15,38; -5,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -4,37</t>
+          <t>-20,59; -6,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-23,66; -7,08</t>
+          <t>-24,96; -7,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -12,72</t>
+          <t>-32,25; -13,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -12,58</t>
+          <t>-45,71; -16,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-4,63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-20,93</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-10,03%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-34,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,3%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-4.627193300420402</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-20.93071484962474</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.309783452383222</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.1003121376126993</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.3480302110097592</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.4229762139167418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-25,47; 14,19</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-39,44; 0,91</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,06; 30,03</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-46,51; 40,62</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-57,04; 4,46</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-35,79; 234,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-25.46592898406701</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-39.4377486977276</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.06055654562587</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.4651482068151507</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5704343164233638</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3579192190731612</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>14.19102721208013</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9133811497210582</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>30.03272700778985</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.4062301926723403</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.04456965179370811</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.34479183433681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-9,56</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-12,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-7,43</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-18,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-22,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-19,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-21,83; 3,66</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-25,6; 1,64</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-30,33; 12,18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-38,36; 8,12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-42,59; 4,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-58,16; 48,81</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-9.556670527653461</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-12.12551496199602</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-7.429320742021456</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1897578820625783</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2252737213806099</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1912037050827199</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,91</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-5,37</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-27,15</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-14,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-51,88%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-21.82944829446316</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-25.59839734903744</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-30.33223843246681</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.38364232840893</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4258983650795721</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5815856976649584</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-14,31; 18,81</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-20,35; 10,68</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-48,05; -3,8</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-23,59; 42,75</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-45,79; 35,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-77,38; -8,36</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.656615591393396</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.642156107554295</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>12.18204482097748</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.08115540797565771</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03995984281461891</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.488127694081869</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-16,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-10,18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-35,63</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-29,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-21,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-60,11%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.908745990598938</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-5.365612764623068</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-27.15240174988468</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.05546846547365726</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1447261793822196</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.5188285143862572</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-31,56; -0,56</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-28,53; 7,27</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-67,58; 3,64</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-51,39; -0,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-51,6; 18,66</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-90,03; 21,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-14.31383310009991</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-20.35252060123223</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-48.05296646903216</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.2359110896794984</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4579131515370021</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.773825796028672</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>18.80581057596094</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.68386021214934</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-3.802261143104477</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.42752819966918</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.354590194537857</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>-0.08361392379639897</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-7,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-8,42</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-7,15</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-13,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-22,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-14,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-28,62; 17,55</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-25,9; 11,01</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-27,62; 16,46</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-45,14; 39,37</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-58,54; 44,52</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-48,25; 44,35</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-16.44264453033533</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-10.17604044688373</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-35.63172300749577</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2975943514015473</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2120310670011257</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.601141580977986</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-17,92</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-17,41</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-36,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-52,41%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-31.55646297235212</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-28.53020019151378</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-67.58261481406153</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5138806831150364</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5159854240091</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9002907987740071</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-11,97; 23,09</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-35,28; -0,38</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-36,71; 4,78</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-24,43; 80,09</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-62,52; -0,13</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-88,67; 29,74</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.5563052058877743</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.272866463233282</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.643698481422306</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.009344330368186386</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1865607942308971</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.210283418037082</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +931,407 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-18,72</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-9,64</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-12,88</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-32,05%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-27,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-28,45%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-7.527101789435192</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-8.418884797683024</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-7.149308887693056</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.1336282417736828</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2285241675063671</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1430742536495942</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-29,42; -6,41</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-19,32; 0,53</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-29,66; 3,53</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-46,51; -12,48</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-49,36; 1,92</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-56,61; 10,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-28.61964142219147</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-25.89710075975013</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-27.62176440924977</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.4513537800784318</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5853787067920252</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4825038781345002</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>17.54645474605307</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.01492363000936</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>16.45962973145769</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.3937126534839273</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4452002072545608</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.4434925219657829</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-6,84</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-8,9</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-18,86</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-11,74%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-17,96%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-48,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-16,26; 5,32</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-18,5; 1,27</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-33,0; -4,09</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-26,24; 9,83</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-33,98; 2,86</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-71,31; -7,45</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>4.321839490885083</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-17.91752550587521</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-17.40983390391167</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1103006265384403</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.3689364900559862</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5241420832079046</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>-8,65</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-10,57</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-13,11</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-16,1%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-23,31%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-31,92%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-11.9698882057878</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-35.28184648489701</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-36.71157273960134</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.2442546195954381</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6252210881486925</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8866696369149504</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-14,05; -4,07</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-15,38; -5,62</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-20,59; -6,23</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>-24,96; -7,88</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-32,25; -13,07</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-45,71; -16,05</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>23.08671185772705</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-0.3813912038833923</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>4.776773815224225</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.8009395291177366</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.001331736741216827</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2973620493221578</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-18.72244097030388</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-9.64403006348798</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-12.88232392150169</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.3204796769621131</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.2760034049272996</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.2845089968669836</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-29.41967530076315</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-19.32078969553475</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-29.65542648309267</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.4651468783721063</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.4935556021527944</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.5660901101843918</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-6.407811650924112</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.5335115541576357</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.53110927230143</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-0.124763284584573</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.01915769436279655</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.1048982428322686</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-6.835555454515896</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-8.902278630267373</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-18.86179532580051</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1173740193970453</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1795598216666488</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.4841379801518746</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-16.25780060326838</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-18.5020786871024</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-33.00398211994307</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.2623759847484337</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.3398308664810956</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.7131064000995413</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>5.318075440189155</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1.26741282776616</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-4.087040209960443</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.09831790868196286</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.02855403482112277</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.07454238988989366</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-8.646016862266686</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-10.57482590979102</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-13.11358105237744</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-0.1610404554092529</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-0.2331172834798522</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-0.3191600958763511</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-14.05485157358868</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-15.3838240810823</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-20.59297094299193</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-0.2495733593773561</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.3225077584074911</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-0.457093758520137</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>-4.067695096038559</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-5.620049701465927</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-6.229699311760297</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-0.07875899032385812</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>-0.1306902523445392</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>-0.1605174301198594</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1340,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Provincia-trans_bre.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-4.627193300420402</v>
+        <v>-3.617780521281233</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-20.93071484962474</v>
+        <v>-15.49791565106632</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>9.309783452383222</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.1003121376126993</v>
+        <v>-0.0765999759388592</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.3480302110097592</v>
+        <v>-0.3075787831867744</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.4229762139167418</v>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-25.46592898406701</v>
+        <v>-19.44081480461978</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-39.4377486977276</v>
+        <v>-31.30017602837943</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>-10.06055654562587</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.4651482068151507</v>
+        <v>-0.3687989260055446</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.5704343164233638</v>
+        <v>-0.5391072765477702</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>-0.3579192190731612</v>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>14.19102721208013</v>
+        <v>11.8617686632821</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.9133811497210582</v>
+        <v>1.860385304851031</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>30.03272700778985</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.4062301926723403</v>
+        <v>0.3198354690628329</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.04456965179370811</v>
+        <v>0.04093425487654364</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>2.34479183433681</v>
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-9.556670527653461</v>
+        <v>-5.89181329635044</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-12.12551496199602</v>
+        <v>-6.01992706519579</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-7.429320742021456</v>
+        <v>-6.548713870101897</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1897578820625783</v>
+        <v>-0.1199944707018623</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2252737213806099</v>
+        <v>-0.1208927804590409</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.1912037050827199</v>
+        <v>-0.1724483904895908</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-21.82944829446316</v>
+        <v>-18.50654420130282</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-25.59839734903744</v>
+        <v>-17.14653486556691</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-30.33223843246681</v>
+        <v>-30.25405274643522</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.38364232840893</v>
+        <v>-0.3443694236140688</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.4258983650795721</v>
+        <v>-0.3164742474876317</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.5815856976649584</v>
+        <v>-0.5975005240222572</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3.656615591393396</v>
+        <v>5.780829856501165</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1.642156107554295</v>
+        <v>5.953658986274093</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>12.18204482097748</v>
+        <v>14.0137097381615</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.08115540797565771</v>
+        <v>0.1348593731419396</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.03995984281461891</v>
+        <v>0.1437991311594502</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.488127694081869</v>
+        <v>0.5176302531540087</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2.908745990598938</v>
+        <v>0.1862356124847087</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-5.365612764623068</v>
+        <v>-4.540173242819312</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-27.15240174988468</v>
+        <v>-30.33506369307376</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.05546846547365726</v>
+        <v>0.00360920125742409</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.1447261793822196</v>
+        <v>-0.1267330632897518</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.5188285143862572</v>
+        <v>-0.560490010022799</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-14.31383310009991</v>
+        <v>-14.72568012988846</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-20.35252060123223</v>
+        <v>-20.61709078477141</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-48.05296646903216</v>
+        <v>-50.03631471717753</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.2359110896794984</v>
+        <v>-0.2576618639117226</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.4579131515370021</v>
+        <v>-0.4670328784888189</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.773825796028672</v>
+        <v>-0.8122314671113299</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>18.80581057596094</v>
+        <v>15.25727395260457</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>10.68386021214934</v>
+        <v>9.190517622384537</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-3.802261143104477</v>
+        <v>-9.721559692122035</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.42752819966918</v>
+        <v>0.3403992977095656</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.354590194537857</v>
+        <v>0.3451424967084497</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>-0.08361392379639897</v>
+        <v>-0.2277835785109105</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-16.44264453033533</v>
+        <v>-20.04311584954875</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-10.17604044688373</v>
+        <v>-15.29838281817066</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-35.63172300749577</v>
+        <v>-41.63383232632145</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.2975943514015473</v>
+        <v>-0.3632699841487016</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2120310670011257</v>
+        <v>-0.3045637364900285</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.601141580977986</v>
+        <v>-0.6440284922091969</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-31.55646297235212</v>
+        <v>-33.76340215964746</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-28.53020019151378</v>
+        <v>-30.57879513181735</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-67.58261481406153</v>
+        <v>-70.80999871505863</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.5138806831150364</v>
+        <v>-0.5660842585606166</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.5159854240091</v>
+        <v>-0.5312129529047671</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.9002907987740071</v>
+        <v>-0.9046838070662685</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>-0.5563052058877743</v>
+        <v>-5.552468571758107</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>7.272866463233282</v>
+        <v>0.7072241384786073</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3.643698481422306</v>
+        <v>-6.509048676406774</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.009344330368186386</v>
+        <v>-0.1259060400534733</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.1865607942308971</v>
+        <v>0.02000831102753423</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.210283418037082</v>
+        <v>-0.1415437946194235</v>
       </c>
     </row>
     <row r="16">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-7.527101789435192</v>
+        <v>4.402629405683756</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-8.418884797683024</v>
+        <v>-7.317582648935189</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-7.149308887693056</v>
+        <v>-7.670515066049527</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.1336282417736828</v>
+        <v>0.09765313569756434</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.2285241675063671</v>
+        <v>-0.2088660577391442</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-0.1430742536495942</v>
+        <v>-0.1512232961271176</v>
       </c>
     </row>
     <row r="17">
@@ -958,22 +958,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-28.61964142219147</v>
+        <v>-14.716465450566</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-25.89710075975013</v>
+        <v>-23.18562070347859</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-27.62176440924977</v>
+        <v>-27.78036915986533</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.4513537800784318</v>
+        <v>-0.2887069806142656</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.5853787067920252</v>
+        <v>-0.5456727393056534</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.4825038781345002</v>
+        <v>-0.4679869828333438</v>
       </c>
     </row>
     <row r="18">
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>17.54645474605307</v>
+        <v>23.96348477644248</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>11.01492363000936</v>
+        <v>13.03252582128566</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>16.45962973145769</v>
+        <v>12.97506660300721</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.3937126534839273</v>
+        <v>0.6775143455790666</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.4452002072545608</v>
+        <v>0.4996932541184267</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.4434925219657829</v>
+        <v>0.3168841096637514</v>
       </c>
     </row>
     <row r="19">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4.321839490885083</v>
+        <v>3.292321736885606</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>-17.91752550587521</v>
+        <v>-19.96742268414845</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-17.40983390391167</v>
+        <v>-11.8998890081315</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.1103006265384403</v>
+        <v>0.07569889952144125</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.3689364900559862</v>
+        <v>-0.4021280515361618</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.5241420832079046</v>
+        <v>-0.3629697697148681</v>
       </c>
     </row>
     <row r="20">
@@ -1040,22 +1040,22 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-11.9698882057878</v>
+        <v>-13.25928789621592</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>-35.28184648489701</v>
+        <v>-35.81797122736879</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-36.71157273960134</v>
+        <v>-33.68093554111985</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.2442546195954381</v>
+        <v>-0.2683135767248565</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.6252210881486925</v>
+        <v>-0.6243818940341526</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.8866696369149504</v>
+        <v>-0.7616574742823535</v>
       </c>
     </row>
     <row r="21">
@@ -1066,22 +1066,22 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>23.08671185772705</v>
+        <v>20.76491703440877</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>-0.3813912038833923</v>
+        <v>-3.931326389434839</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4.776773815224225</v>
+        <v>10.51475566066018</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.8009395291177366</v>
+        <v>0.6301006007909589</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.001331736741216827</v>
+        <v>-0.09319579516519012</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2973620493221578</v>
+        <v>0.6366650041270648</v>
       </c>
     </row>
     <row r="22">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-18.72244097030388</v>
+        <v>-15.64471133948926</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-9.64403006348798</v>
+        <v>-10.77399185239088</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-12.88232392150169</v>
+        <v>-8.596349588925372</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.3204796769621131</v>
+        <v>-0.2781775822920037</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.2760034049272996</v>
+        <v>-0.2958671851992669</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.2845089968669836</v>
+        <v>-0.1968126255464593</v>
       </c>
     </row>
     <row r="23">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-29.41967530076315</v>
+        <v>-25.79733510345626</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-19.32078969553475</v>
+        <v>-21.23632755668671</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-29.65542648309267</v>
+        <v>-23.97125519709891</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-0.4651468783721063</v>
+        <v>-0.4301807623004018</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.4935556021527944</v>
+        <v>-0.5141108734205531</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.5660901101843918</v>
+        <v>-0.4672159059667699</v>
       </c>
     </row>
     <row r="24">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-6.407811650924112</v>
+        <v>-4.244632041424682</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.5335115541576357</v>
+        <v>-1.334927080282101</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3.53110927230143</v>
+        <v>5.710847775885767</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>-0.124763284584573</v>
+        <v>-0.08760796242569428</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.01915769436279655</v>
+        <v>-0.04415953305366008</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1048982428322686</v>
+        <v>0.1579977562864806</v>
       </c>
     </row>
     <row r="25">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>-6.835555454515896</v>
+        <v>-6.505020636423242</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>-8.902278630267373</v>
+        <v>-11.00412767343747</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>-18.86179532580051</v>
+        <v>-17.21964718212817</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1173740193970453</v>
+        <v>-0.1173375591841338</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1795598216666488</v>
+        <v>-0.2205319832370784</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.4841379801518746</v>
+        <v>-0.4527624315226352</v>
       </c>
     </row>
     <row r="26">
@@ -1204,22 +1204,22 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>-16.25780060326838</v>
+        <v>-16.31467830952629</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>-18.5020786871024</v>
+        <v>-20.54109854062033</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-33.00398211994307</v>
+        <v>-29.17249096250261</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.2623759847484337</v>
+        <v>-0.2691927922738375</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.3398308664810956</v>
+        <v>-0.3759697104756024</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.7131064000995413</v>
+        <v>-0.6979968377462412</v>
       </c>
     </row>
     <row r="27">
@@ -1230,22 +1230,22 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>5.318075440189155</v>
+        <v>3.742597094460773</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1.26741282776616</v>
+        <v>-0.3375587764125385</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-4.087040209960443</v>
+        <v>-0.9541738381622851</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.09831790868196286</v>
+        <v>0.07958703708041581</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.02855403482112277</v>
+        <v>-0.006952634149419526</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.07454238988989366</v>
+        <v>-0.04016504421519965</v>
       </c>
     </row>
     <row r="28">
@@ -1260,22 +1260,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-8.646016862266686</v>
+        <v>-7.130798066898336</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-10.57482590979102</v>
+        <v>-10.88127001684109</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-13.11358105237744</v>
+        <v>-12.32099497987068</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>-0.1610404554092529</v>
+        <v>-0.1372871967218577</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.2331172834798522</v>
+        <v>-0.2419034241351145</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.3191600958763511</v>
+        <v>-0.3000036730722092</v>
       </c>
     </row>
     <row r="29">
@@ -1286,22 +1286,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-14.05485157358868</v>
+        <v>-11.55818027409675</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-15.3838240810823</v>
+        <v>-15.66595578458453</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-20.59297094299193</v>
+        <v>-19.56773449867364</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-0.2495733593773561</v>
+        <v>-0.2154209110154637</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.3225077584074911</v>
+        <v>-0.3299600247251513</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.457093758520137</v>
+        <v>-0.433686800202977</v>
       </c>
     </row>
     <row r="30">
@@ -1312,22 +1312,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-4.067695096038559</v>
+        <v>-2.246878864561404</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-5.620049701465927</v>
+        <v>-6.128327594752905</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-6.229699311760297</v>
+        <v>-5.63538401008767</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.07875899032385812</v>
+        <v>-0.04450487681209975</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.1306902523445392</v>
+        <v>-0.1462447275305425</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.1605174301198594</v>
+        <v>-0.13944170009337</v>
       </c>
     </row>
     <row r="31">
